--- a/trading/复盘数据库.xlsx
+++ b/trading/复盘数据库.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,14 +749,265 @@
           <t>000692</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>极度高潮</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.0偏弱</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>中央商场</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>600280</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-10.03</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>63959</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>偏弱</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>高潮</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>无符合规则标的</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2626上涨/2468下跌</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>高潮</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.0+3.0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>艾华集团</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>603989</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>+9.99%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>103家</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1961涨/3142跌</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>修复</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>兆易创新</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>603986</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>594.00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>586.04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>7.33</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1961/3142</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.0+1.0</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>172</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2902/2200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>高潮</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
